--- a/data/sample_matrix_complete.xlsx
+++ b/data/sample_matrix_complete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/DroughtSIP/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629F2138-D29E-664A-B83F-150C8E026019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261BA3D4-51AA-5D4B-B6E4-16E589BA214E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32720" yWindow="1760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1271,8 +1271,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1973,7 +1971,7 @@
         <f t="shared" ref="Q4:Q6" si="0">_xlfn.CONCAT("CUE-",M4,"-",N4,"-",O4,"-",P4)</f>
         <v>CUE-JCR-ROS-0hr-1</v>
       </c>
-      <c r="R4" s="91" t="s">
+      <c r="R4" s="44" t="s">
         <v>291</v>
       </c>
       <c r="S4" s="70">
@@ -1982,7 +1980,9 @@
       <c r="T4" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U4" s="70"/>
+      <c r="U4" s="70">
+        <v>45868</v>
+      </c>
       <c r="W4" s="45" t="s">
         <v>88</v>
       </c>
@@ -2122,7 +2122,7 @@
         <f t="shared" si="0"/>
         <v>CUE-JCR-ROS-0hr-2</v>
       </c>
-      <c r="R5" s="91" t="s">
+      <c r="R5" s="44" t="s">
         <v>292</v>
       </c>
       <c r="S5" s="70">
@@ -2131,7 +2131,9 @@
       <c r="T5" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U5" s="70"/>
+      <c r="U5" s="70">
+        <v>45868</v>
+      </c>
       <c r="W5" s="45" t="s">
         <v>89</v>
       </c>
@@ -2271,7 +2273,7 @@
         <f t="shared" si="0"/>
         <v>CUE-JCR-ROS-0hr-3</v>
       </c>
-      <c r="R6" s="91" t="s">
+      <c r="R6" s="44" t="s">
         <v>293</v>
       </c>
       <c r="S6" s="70">
@@ -2280,7 +2282,9 @@
       <c r="T6" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U6" s="70"/>
+      <c r="U6" s="70">
+        <v>45868</v>
+      </c>
       <c r="W6" s="45" t="s">
         <v>90</v>
       </c>
@@ -2420,14 +2424,16 @@
         <f t="shared" ref="Q7:Q9" si="8">_xlfn.CONCAT("CUE-",M7,"-",N7,"-",O7,"-",P7)</f>
         <v>CUE-JCR-ROS-24hr-1</v>
       </c>
-      <c r="R7" s="91"/>
+      <c r="R7" s="44"/>
       <c r="S7" s="70">
         <v>45782.5</v>
       </c>
       <c r="T7" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U7" s="70"/>
+      <c r="U7" s="70">
+        <v>45868</v>
+      </c>
       <c r="W7" s="45" t="s">
         <v>91</v>
       </c>
@@ -2567,14 +2573,16 @@
         <f t="shared" si="8"/>
         <v>CUE-JCR-ROS-24hr-2</v>
       </c>
-      <c r="R8" s="91"/>
+      <c r="R8" s="44"/>
       <c r="S8" s="70">
         <v>45782.5</v>
       </c>
       <c r="T8" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U8" s="70"/>
+      <c r="U8" s="70">
+        <v>45868</v>
+      </c>
       <c r="W8" s="45" t="s">
         <v>92</v>
       </c>
@@ -2714,14 +2722,16 @@
         <f t="shared" si="8"/>
         <v>CUE-JCR-ROS-24hr-3</v>
       </c>
-      <c r="R9" s="91"/>
+      <c r="R9" s="44"/>
       <c r="S9" s="70">
         <v>45782.5</v>
       </c>
       <c r="T9" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U9" s="70"/>
+      <c r="U9" s="70">
+        <v>45868</v>
+      </c>
       <c r="W9" s="48" t="s">
         <v>93</v>
       </c>
@@ -2861,14 +2871,16 @@
         <f t="shared" ref="Q10:Q21" si="9">_xlfn.CONCAT("CUE-",M10,"-",N10,"-",O10,"-",P10)</f>
         <v>CUE-JCR-ROS-72hr-1</v>
       </c>
-      <c r="R10" s="91"/>
+      <c r="R10" s="44"/>
       <c r="S10" s="70">
         <v>45782.5</v>
       </c>
       <c r="T10" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U10" s="70"/>
+      <c r="U10" s="70">
+        <v>45868</v>
+      </c>
       <c r="W10" s="45" t="s">
         <v>97</v>
       </c>
@@ -3004,14 +3016,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-ROS-72hr-2</v>
       </c>
-      <c r="R11" s="91"/>
+      <c r="R11" s="44"/>
       <c r="S11" s="70">
         <v>45782.5</v>
       </c>
       <c r="T11" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U11" s="70"/>
+      <c r="U11" s="70">
+        <v>45868</v>
+      </c>
       <c r="W11" s="45" t="s">
         <v>98</v>
       </c>
@@ -3147,14 +3161,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-ROS-72hr-3</v>
       </c>
-      <c r="R12" s="91"/>
+      <c r="R12" s="44"/>
       <c r="S12" s="70">
         <v>45782.5</v>
       </c>
       <c r="T12" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U12" s="70"/>
+      <c r="U12" s="70">
+        <v>45868</v>
+      </c>
       <c r="W12" s="45" t="s">
         <v>99</v>
       </c>
@@ -3290,14 +3306,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-0hr-1</v>
       </c>
-      <c r="R13" s="91"/>
+      <c r="R13" s="44"/>
       <c r="S13" s="70">
         <v>45782.5</v>
       </c>
       <c r="T13" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U13" s="70"/>
+      <c r="U13" s="70">
+        <v>45868</v>
+      </c>
       <c r="W13" s="45" t="s">
         <v>100</v>
       </c>
@@ -3433,14 +3451,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-0hr-2</v>
       </c>
-      <c r="R14" s="91"/>
+      <c r="R14" s="44"/>
       <c r="S14" s="70">
         <v>45782.5</v>
       </c>
       <c r="T14" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U14" s="70"/>
+      <c r="U14" s="70">
+        <v>45868</v>
+      </c>
       <c r="W14" s="45" t="s">
         <v>101</v>
       </c>
@@ -3576,14 +3596,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-0hr-3</v>
       </c>
-      <c r="R15" s="91"/>
+      <c r="R15" s="44"/>
       <c r="S15" s="70">
         <v>45782.5</v>
       </c>
       <c r="T15" s="70">
         <v>45782.5</v>
       </c>
-      <c r="U15" s="70"/>
+      <c r="U15" s="70">
+        <v>45868</v>
+      </c>
       <c r="W15" s="48" t="s">
         <v>102</v>
       </c>
@@ -3719,14 +3741,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-24hr-1</v>
       </c>
-      <c r="R16" s="91"/>
+      <c r="R16" s="44"/>
       <c r="S16" s="70">
         <v>45782.5</v>
       </c>
       <c r="T16" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U16" s="70"/>
+      <c r="U16" s="70">
+        <v>45868</v>
+      </c>
       <c r="W16" s="26" t="s">
         <v>106</v>
       </c>
@@ -3856,14 +3880,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-24hr-2</v>
       </c>
-      <c r="R17" s="91"/>
+      <c r="R17" s="44"/>
       <c r="S17" s="70">
         <v>45782.5</v>
       </c>
       <c r="T17" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U17" s="70"/>
+      <c r="U17" s="70">
+        <v>45868</v>
+      </c>
       <c r="W17" s="26" t="s">
         <v>107</v>
       </c>
@@ -4003,14 +4029,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-24hr-3</v>
       </c>
-      <c r="R18" s="91"/>
+      <c r="R18" s="44"/>
       <c r="S18" s="70">
         <v>45782.5</v>
       </c>
       <c r="T18" s="70">
         <v>45783.5</v>
       </c>
-      <c r="U18" s="70"/>
+      <c r="U18" s="70">
+        <v>45868</v>
+      </c>
       <c r="W18" s="26" t="s">
         <v>108</v>
       </c>
@@ -4150,14 +4178,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-72hr-1</v>
       </c>
-      <c r="R19" s="91"/>
+      <c r="R19" s="44"/>
       <c r="S19" s="70">
         <v>45782.5</v>
       </c>
       <c r="T19" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U19" s="70"/>
+      <c r="U19" s="70">
+        <v>45868</v>
+      </c>
       <c r="W19" s="26" t="s">
         <v>109</v>
       </c>
@@ -4297,14 +4327,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-72hr-2</v>
       </c>
-      <c r="R20" s="91"/>
+      <c r="R20" s="44"/>
       <c r="S20" s="70">
         <v>45782.5</v>
       </c>
       <c r="T20" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U20" s="70"/>
+      <c r="U20" s="70">
+        <v>45868</v>
+      </c>
       <c r="W20" s="26" t="s">
         <v>110</v>
       </c>
@@ -4444,14 +4476,16 @@
         <f t="shared" si="9"/>
         <v>CUE-JCR-SKY-72hr-3</v>
       </c>
-      <c r="R21" s="91"/>
+      <c r="R21" s="44"/>
       <c r="S21" s="70">
         <v>45782.5</v>
       </c>
       <c r="T21" s="70">
         <v>45785.5</v>
       </c>
-      <c r="U21" s="70"/>
+      <c r="U21" s="70">
+        <v>45868</v>
+      </c>
       <c r="W21" s="29" t="s">
         <v>111</v>
       </c>
@@ -4591,14 +4625,16 @@
         <f t="shared" ref="Q22:Q27" si="13">_xlfn.CONCAT("CUE-",M22,"-",N22,"-",O22,"-",P22)</f>
         <v>CUE-LOM-ROS-0hr-1</v>
       </c>
-      <c r="R22" s="92"/>
+      <c r="R22" s="4"/>
       <c r="S22" s="57">
         <v>45782.5</v>
       </c>
       <c r="T22" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U22" s="57"/>
+      <c r="U22" s="57">
+        <v>45868</v>
+      </c>
       <c r="W22" s="26" t="s">
         <v>115</v>
       </c>
@@ -4738,14 +4774,16 @@
         <f t="shared" si="13"/>
         <v>CUE-LOM-ROS-0hr-2</v>
       </c>
-      <c r="R23" s="92"/>
+      <c r="R23" s="4"/>
       <c r="S23" s="57">
         <v>45782.5</v>
       </c>
       <c r="T23" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U23" s="57"/>
+      <c r="U23" s="57">
+        <v>45868</v>
+      </c>
       <c r="W23" s="26" t="s">
         <v>116</v>
       </c>
@@ -4881,14 +4919,16 @@
         <f t="shared" si="13"/>
         <v>CUE-LOM-ROS-0hr-3</v>
       </c>
-      <c r="R24" s="92"/>
+      <c r="R24" s="4"/>
       <c r="S24" s="57">
         <v>45782.5</v>
       </c>
       <c r="T24" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U24" s="57"/>
+      <c r="U24" s="57">
+        <v>45868</v>
+      </c>
       <c r="W24" s="26" t="s">
         <v>117</v>
       </c>
@@ -5024,14 +5064,16 @@
         <f t="shared" si="13"/>
         <v>CUE-LOM-ROS-24hr-1</v>
       </c>
-      <c r="R25" s="92"/>
+      <c r="R25" s="4"/>
       <c r="S25" s="57">
         <v>45782.5</v>
       </c>
       <c r="T25" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U25" s="57"/>
+      <c r="U25" s="57">
+        <v>45868</v>
+      </c>
       <c r="W25" s="26" t="s">
         <v>118</v>
       </c>
@@ -5167,14 +5209,16 @@
         <f t="shared" si="13"/>
         <v>CUE-LOM-ROS-24hr-2</v>
       </c>
-      <c r="R26" s="92"/>
+      <c r="R26" s="4"/>
       <c r="S26" s="57">
         <v>45782.5</v>
       </c>
       <c r="T26" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U26" s="57"/>
+      <c r="U26" s="57">
+        <v>45868</v>
+      </c>
       <c r="W26" s="26" t="s">
         <v>119</v>
       </c>
@@ -5310,14 +5354,16 @@
         <f t="shared" si="13"/>
         <v>CUE-LOM-ROS-24hr-3</v>
       </c>
-      <c r="R27" s="92"/>
+      <c r="R27" s="4"/>
       <c r="S27" s="57">
         <v>45782.5</v>
       </c>
       <c r="T27" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U27" s="57"/>
+      <c r="U27" s="57">
+        <v>45868</v>
+      </c>
       <c r="W27" s="29" t="s">
         <v>120</v>
       </c>
@@ -5453,14 +5499,16 @@
         <f t="shared" ref="Q28:Q39" si="16">_xlfn.CONCAT("CUE-",M28,"-",N28,"-",O28,"-",P28)</f>
         <v>CUE-LOM-ROS-72hr-1</v>
       </c>
-      <c r="R28" s="92"/>
+      <c r="R28" s="4"/>
       <c r="S28" s="57">
         <v>45782.5</v>
       </c>
       <c r="T28" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U28" s="57"/>
+      <c r="U28" s="57">
+        <v>45868</v>
+      </c>
       <c r="Y28" s="75"/>
       <c r="Z28" s="75"/>
       <c r="AA28" s="75"/>
@@ -5584,14 +5632,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-ROS-72hr-2</v>
       </c>
-      <c r="R29" s="92"/>
+      <c r="R29" s="4"/>
       <c r="S29" s="57">
         <v>45782.5</v>
       </c>
       <c r="T29" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U29" s="57"/>
+      <c r="U29" s="57">
+        <v>45868</v>
+      </c>
       <c r="Y29" s="75"/>
       <c r="Z29" s="75"/>
       <c r="AA29" s="75"/>
@@ -5705,14 +5755,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-ROS-72hr-3</v>
       </c>
-      <c r="R30" s="92"/>
+      <c r="R30" s="4"/>
       <c r="S30" s="57">
         <v>45782.5</v>
       </c>
       <c r="T30" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U30" s="57"/>
+      <c r="U30" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK30" s="30" t="s">
         <v>6</v>
       </c>
@@ -5801,14 +5853,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-0hr-1</v>
       </c>
-      <c r="R31" s="92"/>
+      <c r="R31" s="4"/>
       <c r="S31" s="57">
         <v>45782.5</v>
       </c>
       <c r="T31" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U31" s="57"/>
+      <c r="U31" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK31" s="33" t="s">
         <v>6</v>
       </c>
@@ -5897,14 +5951,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-0hr-2</v>
       </c>
-      <c r="R32" s="92"/>
+      <c r="R32" s="4"/>
       <c r="S32" s="57">
         <v>45782.5</v>
       </c>
       <c r="T32" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U32" s="57"/>
+      <c r="U32" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK32" s="36" t="s">
         <v>6</v>
       </c>
@@ -5993,14 +6049,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-0hr-3</v>
       </c>
-      <c r="R33" s="92"/>
+      <c r="R33" s="4"/>
       <c r="S33" s="57">
         <v>45782.5</v>
       </c>
       <c r="T33" s="57">
         <v>45782.5</v>
       </c>
-      <c r="U33" s="57"/>
+      <c r="U33" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK33" s="30" t="s">
         <v>6</v>
       </c>
@@ -6089,14 +6147,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-24hr-1</v>
       </c>
-      <c r="R34" s="92"/>
+      <c r="R34" s="4"/>
       <c r="S34" s="57">
         <v>45782.5</v>
       </c>
       <c r="T34" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U34" s="57"/>
+      <c r="U34" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK34" s="33" t="s">
         <v>6</v>
       </c>
@@ -6185,14 +6245,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-24hr-2</v>
       </c>
-      <c r="R35" s="92"/>
+      <c r="R35" s="4"/>
       <c r="S35" s="57">
         <v>45782.5</v>
       </c>
       <c r="T35" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U35" s="57"/>
+      <c r="U35" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK35" s="36" t="s">
         <v>6</v>
       </c>
@@ -6281,14 +6343,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-24hr-3</v>
       </c>
-      <c r="R36" s="92"/>
+      <c r="R36" s="4"/>
       <c r="S36" s="57">
         <v>45782.5</v>
       </c>
       <c r="T36" s="57">
         <v>45783.5</v>
       </c>
-      <c r="U36" s="57"/>
+      <c r="U36" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK36" s="30" t="s">
         <v>6</v>
       </c>
@@ -6373,14 +6437,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-72hr-1</v>
       </c>
-      <c r="R37" s="92"/>
+      <c r="R37" s="4"/>
       <c r="S37" s="57">
         <v>45782.5</v>
       </c>
       <c r="T37" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U37" s="57"/>
+      <c r="U37" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK37" s="22" t="s">
         <v>6</v>
       </c>
@@ -6465,14 +6531,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-72hr-2</v>
       </c>
-      <c r="R38" s="92"/>
+      <c r="R38" s="4"/>
       <c r="S38" s="57">
         <v>45782.5</v>
       </c>
       <c r="T38" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U38" s="57"/>
+      <c r="U38" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK38" s="25" t="s">
         <v>6</v>
       </c>
@@ -6557,14 +6625,16 @@
         <f t="shared" si="16"/>
         <v>CUE-LOM-SKY-72hr-3</v>
       </c>
-      <c r="R39" s="92"/>
+      <c r="R39" s="4"/>
       <c r="S39" s="57">
         <v>45782.5</v>
       </c>
       <c r="T39" s="57">
         <v>45785.5</v>
       </c>
-      <c r="U39" s="57"/>
+      <c r="U39" s="57">
+        <v>45868</v>
+      </c>
       <c r="AK39" s="27" t="s">
         <v>6</v>
       </c>
